--- a/data/CATALOGO_LCA.xlsx
+++ b/data/CATALOGO_LCA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d52177a9150211f7/rubrica_ENES_Merida/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="11_254BBF17CC517BB5C031F8B840107E71CFCECBAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF215B95-7DB9-4F28-B5F2-8C70B7D7E7FA}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_254BBF17CC517BB5C031F8B840107E71CFCECBAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49EB08A2-5531-483A-ACF2-CF4773B3EAAF}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3990" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLANES 2022-2026" sheetId="1" r:id="rId1"/>
@@ -1635,9 +1635,6 @@
     <t>Químico, Ingeniero Químico, Ambiental, Civil o Biólogo.</t>
   </si>
   <si>
-    <t>aisgnatura</t>
-  </si>
-  <si>
     <t>semestre_grupo</t>
   </si>
   <si>
@@ -1657,6 +1654,9 @@
   </si>
   <si>
     <t>LCA, semestres 5° y 7° (optativas)</t>
+  </si>
+  <si>
+    <t>asignatura</t>
   </si>
 </sst>
 </file>
@@ -19707,7 +19707,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>49</v>
@@ -19716,12 +19716,12 @@
         <v>50</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>58</v>
@@ -19736,7 +19736,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>62</v>
@@ -19751,7 +19751,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>64</v>
@@ -19766,7 +19766,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>68</v>
@@ -19781,7 +19781,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>70</v>
@@ -19796,7 +19796,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>66</v>
@@ -19811,7 +19811,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>73</v>
@@ -19826,7 +19826,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>58</v>
@@ -19841,7 +19841,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>62</v>
@@ -19856,7 +19856,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>64</v>
@@ -19871,7 +19871,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>68</v>
@@ -19886,7 +19886,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>70</v>
@@ -19901,7 +19901,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>66</v>
@@ -19916,7 +19916,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>73</v>
@@ -19931,7 +19931,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>89</v>
@@ -19946,7 +19946,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>91</v>
@@ -19961,7 +19961,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>93</v>
@@ -19976,7 +19976,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>95</v>
@@ -19991,7 +19991,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>97</v>
@@ -20006,7 +20006,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>99</v>
@@ -20021,7 +20021,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>101</v>
@@ -20036,7 +20036,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>237</v>
@@ -20051,7 +20051,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>239</v>
@@ -20066,7 +20066,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>209</v>
@@ -20081,7 +20081,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>119</v>
@@ -20096,7 +20096,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>195</v>
@@ -20111,7 +20111,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>197</v>
@@ -20126,7 +20126,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>199</v>
@@ -20141,7 +20141,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>241</v>
@@ -20156,7 +20156,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>193</v>
@@ -20171,7 +20171,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>117</v>
@@ -20186,7 +20186,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>249</v>
@@ -20201,7 +20201,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>128</v>
@@ -20216,7 +20216,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>251</v>
@@ -20231,7 +20231,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>214</v>
@@ -20246,7 +20246,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>212</v>
@@ -20261,7 +20261,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>130</v>
@@ -20276,7 +20276,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>132</v>
@@ -20291,7 +20291,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>134</v>
@@ -20306,7 +20306,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>137</v>
@@ -20321,7 +20321,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>139</v>
@@ -20336,7 +20336,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>141</v>
@@ -20351,7 +20351,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>143</v>
@@ -20366,7 +20366,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>145</v>
@@ -20381,7 +20381,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>147</v>
@@ -20396,7 +20396,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>149</v>
@@ -20411,7 +20411,7 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>217</v>
@@ -20426,7 +20426,7 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>151</v>
@@ -20441,7 +20441,7 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>153</v>
@@ -20456,7 +20456,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>155</v>
@@ -20471,7 +20471,7 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>157</v>
@@ -20486,7 +20486,7 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>159</v>
@@ -20501,7 +20501,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>161</v>
@@ -20516,7 +20516,7 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>163</v>
@@ -20531,7 +20531,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>165</v>
@@ -20546,7 +20546,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>167</v>
@@ -20561,7 +20561,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>169</v>
@@ -20576,7 +20576,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>171</v>
@@ -20591,7 +20591,7 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>173</v>
@@ -20606,7 +20606,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>175</v>
@@ -20621,7 +20621,7 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>219</v>
@@ -20636,7 +20636,7 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>221</v>
@@ -20651,7 +20651,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>223</v>
@@ -20666,7 +20666,7 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>225</v>
@@ -20681,7 +20681,7 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>235</v>
@@ -20696,7 +20696,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>227</v>
@@ -20711,7 +20711,7 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>229</v>
@@ -20726,7 +20726,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>231</v>
@@ -20741,7 +20741,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>233</v>
@@ -20756,7 +20756,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>177</v>

--- a/data/CATALOGO_LCA.xlsx
+++ b/data/CATALOGO_LCA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d52177a9150211f7/rubrica_ENES_Merida/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_254BBF17CC517BB5C031F8B840107E71CFCECBAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49EB08A2-5531-483A-ACF2-CF4773B3EAAF}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="11_254BBF17CC517BB5C031F8B840107E71CFCECBAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BE03B14-8A42-4CFE-8231-E25959C40E8C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLANES 2022-2026" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="perfiles" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">catalogo!$A$1:$S$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">catalogo!$A$1:$S$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LCA!$A$1:$Z$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">LCA_ECOTEC!$A$1:$Z$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LCA_SOCIOECO!$A$1:$Z$80</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3143" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="540">
   <si>
     <t>#</t>
   </si>
@@ -1347,9 +1347,6 @@
     <t>c0707</t>
   </si>
   <si>
-    <t>Especialista con experiencia en implementación práctica de ecotecnias.</t>
-  </si>
-  <si>
     <t>c0704</t>
   </si>
   <si>
@@ -1657,6 +1654,21 @@
   </si>
   <si>
     <t>asignatura</t>
+  </si>
+  <si>
+    <t>INA</t>
+  </si>
+  <si>
+    <t>0938 TEMAS SELECTOS EN CIENCIAS AMBIENTALES II (Mamiferos Marinos)</t>
+  </si>
+  <si>
+    <t>0939 TEMAS SELECTOS EN CIENCIAS AMBIENTALES III (Manejo integrado de ecosistemas: conservación, restauración y aprovechamiento sostenible)</t>
+  </si>
+  <si>
+    <t>0945 TEMAS SELECTOS EN CIENCIAS AMBIENTALES IX (Ecología química marina)</t>
+  </si>
+  <si>
+    <t>FUNDAMENTOS DE INVESTIGACION EN CIENCIAS AMBIENTALES I</t>
   </si>
 </sst>
 </file>
@@ -1678,21 +1690,25 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1709,6 +1725,7 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1798,7 +1815,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -15459,7 +15485,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="12.75" customHeight="1">
+    <row r="36" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>181</v>
       </c>
@@ -15494,7 +15520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="12.75" customHeight="1">
+    <row r="37" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A37" s="11" t="s">
         <v>181</v>
       </c>
@@ -15529,7 +15555,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="12.75" customHeight="1">
+    <row r="38" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A38" s="11" t="s">
         <v>181</v>
       </c>
@@ -15564,7 +15590,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="12.75" customHeight="1">
+    <row r="39" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A39" s="11" t="s">
         <v>181</v>
       </c>
@@ -15599,7 +15625,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="12.75" customHeight="1">
+    <row r="40" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A40" s="11" t="s">
         <v>181</v>
       </c>
@@ -15634,7 +15660,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="12.75" customHeight="1">
+    <row r="41" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A41" s="11" t="s">
         <v>181</v>
       </c>
@@ -15844,7 +15870,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="12.75" customHeight="1">
+    <row r="47" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A47" s="11" t="s">
         <v>181</v>
       </c>
@@ -15879,7 +15905,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="12.75" customHeight="1">
+    <row r="48" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A48" s="11" t="s">
         <v>181</v>
       </c>
@@ -15914,7 +15940,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="12.75" customHeight="1">
+    <row r="49" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A49" s="11" t="s">
         <v>181</v>
       </c>
@@ -15949,7 +15975,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="12.75" customHeight="1">
+    <row r="50" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A50" s="11" t="s">
         <v>181</v>
       </c>
@@ -15984,7 +16010,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="12.75" customHeight="1">
+    <row r="51" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A51" s="11" t="s">
         <v>181</v>
       </c>
@@ -16019,7 +16045,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="12.75" customHeight="1">
+    <row r="52" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A52" s="11" t="s">
         <v>181</v>
       </c>
@@ -16054,7 +16080,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="12.75" customHeight="1">
+    <row r="53" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A53" s="11" t="s">
         <v>181</v>
       </c>
@@ -16089,7 +16115,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="12.75" customHeight="1">
+    <row r="54" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A54" s="11" t="s">
         <v>181</v>
       </c>
@@ -16124,7 +16150,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="12.75" customHeight="1">
+    <row r="55" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A55" s="11" t="s">
         <v>181</v>
       </c>
@@ -16159,7 +16185,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="12.75" customHeight="1">
+    <row r="56" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A56" s="11" t="s">
         <v>181</v>
       </c>
@@ -16194,7 +16220,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="12.75" customHeight="1">
+    <row r="57" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A57" s="11" t="s">
         <v>181</v>
       </c>
@@ -16229,7 +16255,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="12.75" customHeight="1">
+    <row r="58" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A58" s="11" t="s">
         <v>181</v>
       </c>
@@ -16264,7 +16290,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="12.75" customHeight="1">
+    <row r="59" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A59" s="11" t="s">
         <v>181</v>
       </c>
@@ -16299,7 +16325,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="12.75" customHeight="1">
+    <row r="60" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A60" s="11" t="s">
         <v>181</v>
       </c>
@@ -16334,7 +16360,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="12.75" customHeight="1">
+    <row r="61" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A61" s="11" t="s">
         <v>181</v>
       </c>
@@ -16369,7 +16395,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="12.75" customHeight="1">
+    <row r="62" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>181</v>
       </c>
@@ -16404,7 +16430,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="12.75" customHeight="1">
+    <row r="63" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A63" s="11" t="s">
         <v>181</v>
       </c>
@@ -16439,7 +16465,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="12.75" customHeight="1">
+    <row r="64" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A64" s="11" t="s">
         <v>181</v>
       </c>
@@ -16474,7 +16500,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="12.75" customHeight="1">
+    <row r="65" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A65" s="11" t="s">
         <v>181</v>
       </c>
@@ -16509,7 +16535,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="12.75" customHeight="1">
+    <row r="66" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A66" s="11" t="s">
         <v>181</v>
       </c>
@@ -16544,7 +16570,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="12.75" customHeight="1">
+    <row r="67" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A67" s="11" t="s">
         <v>181</v>
       </c>
@@ -16579,7 +16605,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="12.75" customHeight="1">
+    <row r="68" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A68" s="11" t="s">
         <v>181</v>
       </c>
@@ -16614,7 +16640,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="12.75" customHeight="1">
+    <row r="69" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A69" s="11" t="s">
         <v>181</v>
       </c>
@@ -16649,7 +16675,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="12.75" customHeight="1">
+    <row r="70" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A70" s="11" t="s">
         <v>181</v>
       </c>
@@ -16672,7 +16698,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="12.75" customHeight="1">
+    <row r="71" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A71" s="11" t="s">
         <v>181</v>
       </c>
@@ -16695,7 +16721,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="12.75" customHeight="1">
+    <row r="72" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A72" s="11" t="s">
         <v>181</v>
       </c>
@@ -16718,7 +16744,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="12.75" customHeight="1">
+    <row r="73" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A73" s="11" t="s">
         <v>181</v>
       </c>
@@ -16741,7 +16767,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="12.75" customHeight="1">
+    <row r="74" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A74" s="11" t="s">
         <v>181</v>
       </c>
@@ -16764,7 +16790,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="12.75" customHeight="1">
+    <row r="75" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A75" s="11" t="s">
         <v>181</v>
       </c>
@@ -16787,7 +16813,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="12.75" customHeight="1">
+    <row r="76" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A76" s="11" t="s">
         <v>181</v>
       </c>
@@ -16810,7 +16836,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="12.75" customHeight="1">
+    <row r="77" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A77" s="11" t="s">
         <v>181</v>
       </c>
@@ -16833,7 +16859,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="12.75" customHeight="1">
+    <row r="78" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A78" s="11" t="s">
         <v>181</v>
       </c>
@@ -16856,7 +16882,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="12.75" customHeight="1">
+    <row r="79" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A79" s="11" t="s">
         <v>181</v>
       </c>
@@ -19678,11 +19704,8 @@
   <autoFilter ref="A1:Z80" xr:uid="{00000000-0009-0000-0000-000002000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="10"/>
         <filter val="5"/>
-        <filter val="6"/>
         <filter val="7"/>
-        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -19697,17 +19720,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="3" max="3" width="101.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="95.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>49</v>
@@ -19716,12 +19739,12 @@
         <v>50</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>58</v>
@@ -19736,7 +19759,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>62</v>
@@ -19751,7 +19774,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>64</v>
@@ -19766,37 +19789,37 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>69</v>
+        <v>254</v>
       </c>
       <c r="D5" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>0104 INTRODUCCION A CIENCIAS AMBIENTALES</v>
+        <v>0104 INTRODUCCION A LAS CIENCIAS AMBIENTALES</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="D6" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>0105 INTRODUCCION A CIENCIAS SOCIALES</v>
+        <v>0105 INTRODUCCION A LAS CIENCIAS SOCIALES</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>66</v>
@@ -19811,7 +19834,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>73</v>
@@ -19826,7 +19849,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>58</v>
@@ -19835,13 +19858,13 @@
         <v>59</v>
       </c>
       <c r="D9" s="11" t="str">
-        <f t="shared" ref="D9:D71" si="1">CONCATENATE(B9," ",C9)</f>
+        <f t="shared" ref="D9:D38" si="1">CONCATENATE(B9," ",C9)</f>
         <v>0100 FISICA Y QUIMICA AMBIENTAL</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>62</v>
@@ -19856,7 +19879,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>64</v>
@@ -19871,37 +19894,37 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>68</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>69</v>
+        <v>254</v>
       </c>
       <c r="D12" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>0104 INTRODUCCION A CIENCIAS AMBIENTALES</v>
+        <v>0104 INTRODUCCION A LAS CIENCIAS AMBIENTALES</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>70</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="D13" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>0105 INTRODUCCION A CIENCIAS SOCIALES</v>
+        <v>0105 INTRODUCCION A LAS CIENCIAS SOCIALES</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>66</v>
@@ -19916,7 +19939,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>73</v>
@@ -19931,22 +19954,22 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>89</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>90</v>
+        <v>539</v>
       </c>
       <c r="D16" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>0300 FUNDAM.INVEST. EN CIENCIAS AMBIEN. I</v>
+        <v>0300 FUNDAMENTOS DE INVESTIGACION EN CIENCIAS AMBIENTALES I</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>91</v>
@@ -19961,22 +19984,22 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>93</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
       <c r="D18" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>0302 HIDROLOGIA Y ENERGETICA DEL ECOSIST</v>
+        <v>0302 HIDROLOGIA Y ENERGETICA DEL ECOSISTEMA</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>95</v>
@@ -19991,7 +20014,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>97</v>
@@ -20006,7 +20029,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>99</v>
@@ -20021,7 +20044,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>101</v>
@@ -20036,7 +20059,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>237</v>
@@ -20051,7 +20074,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>239</v>
@@ -20066,7 +20089,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>209</v>
@@ -20081,7 +20104,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>119</v>
@@ -20096,7 +20119,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>195</v>
@@ -20111,7 +20134,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>197</v>
@@ -20126,7 +20149,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>199</v>
@@ -20141,7 +20164,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>241</v>
@@ -20156,7 +20179,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>193</v>
@@ -20171,7 +20194,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>117</v>
@@ -20186,7 +20209,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>249</v>
@@ -20201,7 +20224,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>128</v>
@@ -20216,22 +20239,22 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>251</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="D35" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>0703 ECOTECNOLOGIA</v>
+        <v>0703 ECOTECNOLOGÍA</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>214</v>
@@ -20246,7 +20269,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>212</v>
@@ -20261,7 +20284,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>130</v>
@@ -20276,498 +20299,207 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D39" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0800 INGLES 8</v>
+        <f>CONCATENATE(B39," ",C39)</f>
+        <v>0007 ECOLOGIA EVOLUTIVA</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="D40" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0001 BIOTECNOLOGIA</v>
+        <f>CONCATENATE(B40," ",C40)</f>
+        <v>0010 INTRODUCCION A LA ESCRITURA DE TEXTOS CIENTIFICOS</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="D41" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0002 CALIDAD DEL AGUA</v>
+        <f>CONCATENATE(B41," ",C41)</f>
+        <v>0014 LABORATORIO DE SISTEMAS DE INFORMACION GEOGRAFICA</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="D42" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0003 DIVERSIDAD DE LOS ARBOLES TROPICALES EN MEXICO</v>
+        <f>CONCATENATE(B42," ",C42)</f>
+        <v>0019 REGENERACION Y RESTAURACION EN AMBIENTES TROPICALES</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="D43" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0004 ECOFISIOLOGIA DE LAS PLANTAS</v>
+        <f>CONCATENATE(B43," ",C43)</f>
+        <v>0020 TALLER DE BASES DE DATOS</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>143</v>
+        <v>221</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D44" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0005 ECOLOGIA DEL PAISAJE</v>
+        <v>222</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>145</v>
+        <v>223</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D45" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0006 ECOLOGIA DEL SUELO Y BIOGEOQUIMICA</v>
+        <v>224</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>147</v>
+        <v>235</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D46" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0007 ECOLOGIA EVOLUTIVA</v>
+        <v>236</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="D47" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0008 ECOLOGIA URBANA</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>534</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D48" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0094 ECOLOGÍA Y CONSERVACIÓN DE LAS SELVAS TROPICALES</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0009 ECOLOGIA Y CONSERVACION DEL BOSQUE TROPICAL CADUCIFOLIO</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>534</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D50" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0010 INTRODUCCION A LA ESCRITURA DE TEXTOS CIENTIFICOS</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>534</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D51" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0011 INTRODUCCION A METODOS MULTIVARIADOS</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>534</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0012 INTRODUCCION AL LENGUAJE "R"</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>534</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D53" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0013 INVASIONES BIOTICAS</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>534</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D54" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0014 LABORATORIO DE SISTEMAS DE INFORMACION GEOGRAFICA</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>534</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0015 MEDIOS AUDIOVISUALES Y COMUNICACION AMBIENTAL</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>534</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D56" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0016 METODOS NO PARAMETRICOS</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
-        <v>534</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D57" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0017 PERIODISMO AMBIENTAL</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>534</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D58" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0018 PLANIFICACION AMBIENTAL</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>534</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D59" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0019 REGENERACION Y RESTAURACION EN AMBIENTES TROPICALES</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
-        <v>534</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D60" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0020 TALLER DE BASES DE DATOS</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
-        <v>534</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D61" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0021 TECNICAS SELECTAS EN ECOLOGIA VEGETAL CUANTITATIVA</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
-        <v>534</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D62" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0937 TEMAS SELEC.EN CIENCIAS AMBIENT.I</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" t="s">
-        <v>534</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D63" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0938 TEMAS SELEC.EN CIENCIAS AMBIENT.II</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>534</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D64" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0939 TEMAS SELEC.EN CIENCIAS AMBIENT.III</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>534</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="D65" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0940 TEMAS SELEC.EN CIENCIAS AMBIENT.IV</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
-        <v>534</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="D66" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0945 TEMAS SELEC.EN CIENCIAS AMBIENT.IX</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
-        <v>534</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="D67" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0941 TEMAS SELEC.EN CIENCIAS AMBIENT.V</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" t="s">
-        <v>534</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D68" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0942 TEMAS SELEC.EN CIENCIAS AMBIENT.VI</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
-        <v>534</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="D69" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0943 TEMAS SELEC.EN CIENCIAS AMBIENT.VII</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>534</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="D70" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>0944 TEMAS SELEC.EN CIENCIAS AMBIENT.VIII</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
-        <v>534</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D71" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B47," ",C47)</f>
         <v>0022 TRATAMIENTO DE AGUA</v>
       </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="12"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="12"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="12"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="12"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="12"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="12"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="12"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="12"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="12"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="12"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="12"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="12"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="12"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="12"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="12"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="12"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="12"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="12"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="12"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="12"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="12"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="12"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="12"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="12"/>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" s="12"/>
@@ -20793,80 +20525,12 @@
     <row r="88" spans="2:2">
       <c r="B88" s="12"/>
     </row>
-    <row r="89" spans="2:2">
-      <c r="B89" s="12"/>
-    </row>
-    <row r="90" spans="2:2">
-      <c r="B90" s="12"/>
-    </row>
-    <row r="91" spans="2:2">
-      <c r="B91" s="12"/>
-    </row>
-    <row r="92" spans="2:2">
-      <c r="B92" s="12"/>
-    </row>
-    <row r="93" spans="2:2">
-      <c r="B93" s="12"/>
-    </row>
-    <row r="94" spans="2:2">
-      <c r="B94" s="12"/>
-    </row>
-    <row r="95" spans="2:2">
-      <c r="B95" s="12"/>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96" s="12"/>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="12"/>
-    </row>
-    <row r="98" spans="2:2">
-      <c r="B98" s="12"/>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="12"/>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" s="12"/>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101" s="12"/>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102" s="12"/>
-    </row>
-    <row r="103" spans="2:2">
-      <c r="B103" s="12"/>
-    </row>
-    <row r="104" spans="2:2">
-      <c r="B104" s="12"/>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" s="12"/>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106" s="12"/>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107" s="12"/>
-    </row>
-    <row r="108" spans="2:2">
-      <c r="B108" s="12"/>
-    </row>
-    <row r="109" spans="2:2">
-      <c r="B109" s="12"/>
-    </row>
-    <row r="110" spans="2:2">
-      <c r="B110" s="12"/>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111" s="12"/>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="12"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S80" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:S56" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A39:D47">
+      <sortCondition sortBy="cellColor" ref="A1:A56" dxfId="0"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -22119,7 +21783,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="12.75" customHeight="1">
+    <row r="36" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>253</v>
       </c>
@@ -22154,7 +21818,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="12.75" customHeight="1">
+    <row r="37" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A37" s="11" t="s">
         <v>253</v>
       </c>
@@ -22189,7 +21853,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="12.75" customHeight="1">
+    <row r="38" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A38" s="11" t="s">
         <v>253</v>
       </c>
@@ -22224,7 +21888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="12.75" customHeight="1">
+    <row r="39" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A39" s="11" t="s">
         <v>253</v>
       </c>
@@ -22259,7 +21923,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="12.75" customHeight="1">
+    <row r="40" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A40" s="11" t="s">
         <v>253</v>
       </c>
@@ -22294,7 +21958,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="12.75" customHeight="1">
+    <row r="41" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A41" s="11" t="s">
         <v>253</v>
       </c>
@@ -22504,7 +22168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="12.75" customHeight="1">
+    <row r="47" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A47" s="11" t="s">
         <v>253</v>
       </c>
@@ -22539,7 +22203,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="12.75" customHeight="1">
+    <row r="48" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A48" s="11" t="s">
         <v>253</v>
       </c>
@@ -22574,7 +22238,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="12.75" customHeight="1">
+    <row r="49" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A49" s="11" t="s">
         <v>253</v>
       </c>
@@ -22609,7 +22273,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="12.75" customHeight="1">
+    <row r="50" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A50" s="11" t="s">
         <v>253</v>
       </c>
@@ -22644,7 +22308,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="12.75" customHeight="1">
+    <row r="51" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A51" s="11" t="s">
         <v>253</v>
       </c>
@@ -22679,7 +22343,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="12.75" customHeight="1">
+    <row r="52" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A52" s="11" t="s">
         <v>253</v>
       </c>
@@ -22714,7 +22378,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="12.75" customHeight="1">
+    <row r="53" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A53" s="11" t="s">
         <v>253</v>
       </c>
@@ -22749,7 +22413,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="12.75" customHeight="1">
+    <row r="54" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A54" s="11" t="s">
         <v>253</v>
       </c>
@@ -22784,7 +22448,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="12.75" customHeight="1">
+    <row r="55" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A55" s="11" t="s">
         <v>253</v>
       </c>
@@ -22819,7 +22483,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="12.75" customHeight="1">
+    <row r="56" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A56" s="11" t="s">
         <v>253</v>
       </c>
@@ -22854,7 +22518,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="12.75" customHeight="1">
+    <row r="57" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A57" s="11" t="s">
         <v>253</v>
       </c>
@@ -22889,7 +22553,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="12.75" customHeight="1">
+    <row r="58" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A58" s="11" t="s">
         <v>253</v>
       </c>
@@ -22924,7 +22588,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="12.75" customHeight="1">
+    <row r="59" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A59" s="11" t="s">
         <v>253</v>
       </c>
@@ -22959,7 +22623,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="12.75" customHeight="1">
+    <row r="60" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A60" s="11" t="s">
         <v>253</v>
       </c>
@@ -22994,7 +22658,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="12.75" customHeight="1">
+    <row r="61" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A61" s="11" t="s">
         <v>253</v>
       </c>
@@ -23029,7 +22693,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="12.75" customHeight="1">
+    <row r="62" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>253</v>
       </c>
@@ -23064,7 +22728,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="12.75" customHeight="1">
+    <row r="63" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A63" s="11" t="s">
         <v>253</v>
       </c>
@@ -23099,7 +22763,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="12.75" customHeight="1">
+    <row r="64" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A64" s="11" t="s">
         <v>253</v>
       </c>
@@ -23134,7 +22798,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="12.75" customHeight="1">
+    <row r="65" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A65" s="11" t="s">
         <v>253</v>
       </c>
@@ -23169,7 +22833,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="12.75" customHeight="1">
+    <row r="66" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A66" s="11" t="s">
         <v>253</v>
       </c>
@@ -23204,7 +22868,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="12.75" customHeight="1">
+    <row r="67" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A67" s="11" t="s">
         <v>253</v>
       </c>
@@ -23239,7 +22903,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="12.75" customHeight="1">
+    <row r="68" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A68" s="11" t="s">
         <v>253</v>
       </c>
@@ -23274,7 +22938,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="12.75" customHeight="1">
+    <row r="69" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A69" s="11" t="s">
         <v>253</v>
       </c>
@@ -23309,7 +22973,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="12.75" customHeight="1">
+    <row r="70" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A70" s="11" t="s">
         <v>253</v>
       </c>
@@ -23332,7 +22996,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="12.75" customHeight="1">
+    <row r="71" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A71" s="11" t="s">
         <v>253</v>
       </c>
@@ -23355,7 +23019,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="12.75" customHeight="1">
+    <row r="72" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A72" s="11" t="s">
         <v>253</v>
       </c>
@@ -23378,7 +23042,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="12.75" customHeight="1">
+    <row r="73" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A73" s="11" t="s">
         <v>253</v>
       </c>
@@ -23401,7 +23065,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="12.75" customHeight="1">
+    <row r="74" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A74" s="11" t="s">
         <v>253</v>
       </c>
@@ -23424,7 +23088,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="12.75" customHeight="1">
+    <row r="75" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A75" s="11" t="s">
         <v>253</v>
       </c>
@@ -23447,7 +23111,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="12.75" customHeight="1">
+    <row r="76" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A76" s="11" t="s">
         <v>253</v>
       </c>
@@ -23470,7 +23134,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="12.75" customHeight="1">
+    <row r="77" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A77" s="11" t="s">
         <v>253</v>
       </c>
@@ -23493,7 +23157,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="12.75" customHeight="1">
+    <row r="78" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A78" s="11" t="s">
         <v>253</v>
       </c>
@@ -23516,7 +23180,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="12.75" customHeight="1">
+    <row r="79" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A79" s="11" t="s">
         <v>253</v>
       </c>
@@ -26338,11 +26002,8 @@
   <autoFilter ref="A1:Z80" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="10"/>
         <filter val="5"/>
-        <filter val="6"/>
         <filter val="7"/>
-        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -31832,11 +31493,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="78" customWidth="1"/>
-    <col min="3" max="3" width="99.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -31909,7 +31570,7 @@
         <v>288</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L2" s="17" t="s">
         <v>290</v>
@@ -31932,7 +31593,7 @@
         <v>286</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>287</v>
@@ -31941,7 +31602,7 @@
         <v>287</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J3" s="17" t="s">
         <v>289</v>
@@ -31950,7 +31611,7 @@
         <v>287</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -32081,7 +31742,7 @@
         <v>286</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>290</v>
@@ -32093,10 +31754,10 @@
         <v>287</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K7" s="17" t="s">
         <v>289</v>
@@ -32154,13 +31815,13 @@
         <v>293</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>286</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>287</v>
@@ -32169,7 +31830,7 @@
         <v>287</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J9" s="17" t="s">
         <v>289</v>
@@ -32201,19 +31862,19 @@
         <v>287</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H10" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>288</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>289</v>
       </c>
       <c r="J10" s="17" t="s">
         <v>290</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L10" s="17" t="s">
         <v>286</v>
@@ -32280,16 +31941,16 @@
         <v>287</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>289</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L12" s="17" t="s">
         <v>288</v>
@@ -32344,7 +32005,7 @@
         <v>324</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>287</v>
@@ -32420,19 +32081,19 @@
         <v>330</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>289</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I16" s="17" t="s">
         <v>289</v>
@@ -32441,7 +32102,7 @@
         <v>288</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L16" s="17" t="s">
         <v>286</v>
@@ -32458,7 +32119,7 @@
         <v>333</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>287</v>
@@ -32467,10 +32128,10 @@
         <v>287</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I17" s="17" t="s">
         <v>286</v>
@@ -32479,10 +32140,10 @@
         <v>288</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -32496,7 +32157,7 @@
         <v>336</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>289</v>
@@ -32511,16 +32172,16 @@
         <v>287</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>288</v>
+        <v>535</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>289</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -32578,25 +32239,25 @@
         <v>289</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>287</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K20" s="17" t="s">
         <v>289</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -32619,7 +32280,7 @@
         <v>287</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>286</v>
@@ -32654,25 +32315,25 @@
         <v>288</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>287</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K22" s="17" t="s">
         <v>286</v>
       </c>
       <c r="L22" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -32692,7 +32353,7 @@
         <v>289</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>287</v>
@@ -32701,13 +32362,13 @@
         <v>287</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>286</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L23" s="17" t="s">
         <v>289</v>
@@ -32730,7 +32391,7 @@
         <v>286</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>287</v>
@@ -32762,10 +32423,10 @@
         <v>356</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>287</v>
@@ -32777,16 +32438,16 @@
         <v>287</v>
       </c>
       <c r="I25" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="L25" s="17" t="s">
         <v>289</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="L25" s="17" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -32800,19 +32461,19 @@
         <v>359</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I26" s="17" t="s">
         <v>286</v>
@@ -32821,7 +32482,7 @@
         <v>288</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L26" s="17" t="s">
         <v>289</v>
@@ -32838,28 +32499,28 @@
         <v>330</v>
       </c>
       <c r="D27" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="E27" s="17" t="s">
-        <v>289</v>
-      </c>
       <c r="F27" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G27" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I27" s="17" t="s">
         <v>288</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>289</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>288</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L27" s="17" t="s">
         <v>286</v>
@@ -32923,7 +32584,7 @@
         <v>290</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>287</v>
@@ -32932,7 +32593,7 @@
         <v>288</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K29" s="17" t="s">
         <v>289</v>
@@ -32958,19 +32619,19 @@
         <v>286</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G30" s="17" t="s">
         <v>287</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K30" s="17" t="s">
         <v>287</v>
@@ -32999,10 +32660,10 @@
         <v>287</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I31" s="17" t="s">
         <v>286</v>
@@ -33028,19 +32689,19 @@
         <v>375</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I32" s="17" t="s">
         <v>286</v>
@@ -33049,10 +32710,10 @@
         <v>288</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -33107,7 +32768,7 @@
         <v>289</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>287</v>
@@ -33116,7 +32777,7 @@
         <v>287</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>288</v>
@@ -33151,13 +32812,13 @@
         <v>287</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J35" s="17" t="s">
         <v>288</v>
@@ -33186,7 +32847,7 @@
         <v>288</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G36" s="17" t="s">
         <v>288</v>
@@ -33218,7 +32879,7 @@
         <v>390</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>288</v>
@@ -33233,7 +32894,7 @@
         <v>287</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J37" s="17" t="s">
         <v>289</v>
@@ -33262,13 +32923,13 @@
         <v>289</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I38" s="17" t="s">
         <v>289</v>
@@ -33277,7 +32938,7 @@
         <v>288</v>
       </c>
       <c r="K38" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L38" s="17" t="s">
         <v>286</v>
@@ -33347,13 +33008,13 @@
         <v>287</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J40" s="17" t="s">
         <v>290</v>
       </c>
       <c r="K40" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L40" s="17" t="s">
         <v>289</v>
@@ -33385,16 +33046,16 @@
         <v>287</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J41" s="17" t="s">
         <v>289</v>
       </c>
       <c r="K41" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="L41" s="17" t="s">
         <v>289</v>
-      </c>
-      <c r="L41" s="17" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -33423,13 +33084,13 @@
         <v>287</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J42" s="17" t="s">
         <v>289</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L42" s="17" t="s">
         <v>289</v>
@@ -33446,28 +33107,28 @@
         <v>407</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K43" s="17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="L43" s="17" t="s">
         <v>286</v>
@@ -33493,13 +33154,13 @@
         <v>287</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J44" s="17" t="s">
         <v>290</v>
@@ -33540,10 +33201,10 @@
         <v>290</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="K45" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L45" s="17" t="s">
         <v>289</v>
@@ -33563,25 +33224,25 @@
         <v>288</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J46" s="17" t="s">
         <v>288</v>
       </c>
       <c r="K46" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L46" s="17" t="s">
         <v>286</v>
@@ -33589,51 +33250,51 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="16" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>416</v>
+        <v>296</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G47" s="17" t="s">
         <v>289</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J47" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="L47" s="17" t="s">
         <v>288</v>
-      </c>
-      <c r="K47" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="L47" s="17" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="16" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>296</v>
+        <v>421</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>287</v>
@@ -33645,54 +33306,54 @@
         <v>287</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H48" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I48" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="I48" s="17" t="s">
+      <c r="J48" s="17" t="s">
         <v>290</v>
-      </c>
-      <c r="J48" s="17" t="s">
-        <v>287</v>
       </c>
       <c r="K48" s="17" t="s">
         <v>287</v>
       </c>
       <c r="L48" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="16" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G49" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I49" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="H49" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="I49" s="17" t="s">
+      <c r="J49" s="17" t="s">
         <v>286</v>
-      </c>
-      <c r="J49" s="17" t="s">
-        <v>290</v>
       </c>
       <c r="K49" s="17" t="s">
         <v>287</v>
@@ -33703,75 +33364,75 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="16" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>286</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J50" s="17" t="s">
         <v>286</v>
       </c>
       <c r="K50" s="17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="L50" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="16" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>289</v>
       </c>
       <c r="F51" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I51" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="J51" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="G51" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="H51" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="I51" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="J51" s="17" t="s">
-        <v>288</v>
-      </c>
       <c r="K51" s="17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="L51" s="17" t="s">
         <v>286</v>
@@ -33779,7 +33440,7 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="16" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B52" s="17" t="s">
         <v>429</v>
@@ -33788,7 +33449,7 @@
         <v>430</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>289</v>
@@ -33817,57 +33478,57 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="16" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>215</v>
+        <v>433</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G53" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="I53" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="J53" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="K53" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="H53" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="I53" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="J53" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="K53" s="17" t="s">
-        <v>286</v>
-      </c>
       <c r="L53" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="16" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>435</v>
+        <v>296</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>287</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>287</v>
@@ -33876,27 +33537,27 @@
         <v>289</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J54" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K54" s="17" t="s">
         <v>287</v>
       </c>
       <c r="L54" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="16" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>296</v>
@@ -33931,37 +33592,37 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="16" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>296</v>
+        <v>441</v>
       </c>
       <c r="D56" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="G56" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="H56" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="I56" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="G56" s="17" t="s">
+      <c r="J56" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="H56" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="I56" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="J56" s="17" t="s">
-        <v>287</v>
-      </c>
       <c r="K56" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L56" s="17" t="s">
         <v>288</v>
@@ -33969,16 +33630,16 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="16" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>286</v>
@@ -33996,10 +33657,10 @@
         <v>287</v>
       </c>
       <c r="J57" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K57" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L57" s="17" t="s">
         <v>288</v>
@@ -34007,22 +33668,22 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="16" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>286</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G58" s="17" t="s">
         <v>287</v>
@@ -34031,30 +33692,30 @@
         <v>287</v>
       </c>
       <c r="I58" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="J58" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="K58" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="L58" s="17" t="s">
         <v>290</v>
-      </c>
-      <c r="J58" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="K58" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="L58" s="17" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="16" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>286</v>
@@ -34083,13 +33744,13 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="16" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D60" s="17" t="s">
         <v>288</v>
@@ -34110,27 +33771,27 @@
         <v>287</v>
       </c>
       <c r="J60" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K60" s="17" t="s">
         <v>287</v>
       </c>
       <c r="L60" s="17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="16" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>286</v>
@@ -34159,22 +33820,22 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="16" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>286</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G62" s="17" t="s">
         <v>287</v>
@@ -34183,13 +33844,13 @@
         <v>287</v>
       </c>
       <c r="I62" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="J62" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="J62" s="17" t="s">
-        <v>286</v>
-      </c>
       <c r="K62" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L62" s="17" t="s">
         <v>288</v>
@@ -34197,22 +33858,22 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="16" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G63" s="17" t="s">
         <v>287</v>
@@ -34221,7 +33882,7 @@
         <v>287</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J63" s="17" t="s">
         <v>289</v>
@@ -34230,21 +33891,21 @@
         <v>287</v>
       </c>
       <c r="L63" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="16" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>286</v>
@@ -34259,27 +33920,27 @@
         <v>287</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J64" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K64" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="L64" s="17" t="s">
         <v>290</v>
-      </c>
-      <c r="L64" s="17" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="16" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D65" s="17" t="s">
         <v>288</v>
@@ -34311,89 +33972,89 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="16" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E66" s="17" t="s">
         <v>286</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J66" s="17" t="s">
         <v>286</v>
       </c>
       <c r="K66" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L66" s="17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="16" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D67" s="17" t="s">
         <v>286</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K67" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L67" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="16" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D68" s="17" t="s">
         <v>286</v>
@@ -34402,7 +34063,7 @@
         <v>289</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G68" s="17" t="s">
         <v>287</v>
@@ -34411,13 +34072,13 @@
         <v>287</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K68" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="L68" s="17" t="s">
         <v>289</v>
@@ -34425,57 +34086,57 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" s="16" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D69" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="E69" s="17" t="s">
         <v>286</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>288</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>287</v>
       </c>
       <c r="I69" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="J69" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="L69" s="17" t="s">
         <v>290</v>
-      </c>
-      <c r="J69" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="K69" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="L69" s="17" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" s="16" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D70" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E70" s="17" t="s">
         <v>288</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>286</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>287</v>
@@ -34487,165 +34148,165 @@
         <v>287</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K70" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L70" s="17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="16" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G71" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="H71" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="I71" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="J71" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="H71" s="17" t="s">
+      <c r="K71" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="I71" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="J71" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="K71" s="17" t="s">
+      <c r="L71" s="17" t="s">
         <v>286</v>
-      </c>
-      <c r="L71" s="17" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="16" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D72" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="G72" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="H72" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="F72" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="G72" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="H72" s="17" t="s">
+      <c r="I72" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="J72" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="K72" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="I72" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="J72" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="K72" s="17" t="s">
-        <v>287</v>
-      </c>
       <c r="L72" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="16" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D73" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="G73" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="E73" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="F73" s="17" t="s">
+      <c r="H73" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="I73" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="G73" s="17" t="s">
+      <c r="J73" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="H73" s="17" t="s">
+      <c r="K73" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="I73" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="J73" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="K73" s="17" t="s">
-        <v>289</v>
-      </c>
       <c r="L73" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="16" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G74" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H74" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I74" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="J74" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="K74" s="17" t="s">
         <v>288</v>
-      </c>
-      <c r="H74" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="I74" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="J74" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="K74" s="17" t="s">
-        <v>287</v>
       </c>
       <c r="L74" s="17" t="s">
         <v>286</v>
@@ -34653,57 +34314,57 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="16" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G75" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I75" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="J75" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="K75" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="H75" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="I75" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="J75" s="17" t="s">
+      <c r="L75" s="17" t="s">
         <v>289</v>
-      </c>
-      <c r="K75" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="L75" s="17" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="16" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D76" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E76" s="17" t="s">
         <v>288</v>
-      </c>
-      <c r="E76" s="17" t="s">
-        <v>286</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>287</v>
@@ -34715,13 +34376,13 @@
         <v>287</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J76" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="K76" s="17" t="s">
         <v>286</v>
-      </c>
-      <c r="K76" s="17" t="s">
-        <v>290</v>
       </c>
       <c r="L76" s="17" t="s">
         <v>289</v>
@@ -34729,89 +34390,89 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="16" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D77" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="E77" s="17" t="s">
         <v>286</v>
-      </c>
-      <c r="E77" s="17" t="s">
-        <v>288</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>287</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>287</v>
       </c>
       <c r="I77" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J77" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K77" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L77" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="16" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D78" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="E78" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="E78" s="17" t="s">
-        <v>286</v>
-      </c>
       <c r="F78" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J78" s="17" t="s">
         <v>289</v>
       </c>
       <c r="K78" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L78" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="16" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B79" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="C79" s="17" t="s">
         <v>507</v>
-      </c>
-      <c r="C79" s="17" t="s">
-        <v>508</v>
       </c>
       <c r="D79" s="17" t="s">
         <v>288</v>
@@ -34843,13 +34504,13 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="16" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D80" s="17" t="s">
         <v>288</v>
@@ -34881,13 +34542,13 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="16" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D81" s="17" t="s">
         <v>288</v>
@@ -34919,13 +34580,13 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="16" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D82" s="17" t="s">
         <v>288</v>
@@ -34957,13 +34618,13 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="16" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D83" s="17" t="s">
         <v>288</v>
@@ -34995,13 +34656,13 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D84" s="17" t="s">
         <v>288</v>
@@ -35033,13 +34694,13 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="16" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D85" s="17" t="s">
         <v>288</v>
@@ -35071,13 +34732,13 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="16" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D86" s="17" t="s">
         <v>288</v>
@@ -35109,77 +34770,39 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="16" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="D87" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="E87" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="F87" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="E87" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="F87" s="17" t="s">
+      <c r="G87" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H87" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I87" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="G87" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="H87" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="I87" s="17" t="s">
-        <v>289</v>
-      </c>
       <c r="J87" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K87" s="17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="L87" s="17" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C88" s="17" t="s">
-        <v>527</v>
-      </c>
-      <c r="D88" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="E88" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="F88" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="G88" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="H88" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="I88" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="J88" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="K88" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="L88" s="17" t="s">
         <v>288</v>
       </c>
     </row>
